--- a/travel_agent_forms/014_visa_quotation_request_form--travel_agent_forms.xlsx
+++ b/travel_agent_forms/014_visa_quotation_request_form--travel_agent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'australia',_'label':_'australia'}</t>
+          <t>australia</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Australia', 'label': 'Australia'}</t>
+          <t>Australia</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'canada',_'label':_'canada'}</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Canada', 'label': 'Canada'}</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'united_states',_'label':_'united_states'}</t>
+          <t>united_states</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'United States', 'label': 'United States'}</t>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'tourism',_'label':_'tourism'}</t>
+          <t>tourism</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'tourism', 'label': 'Tourism'}</t>
+          <t>Tourism</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'business',_'label':_'business'}</t>
+          <t>business</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'business', 'label': 'Business'}</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'study',_'label':_'study'}</t>
+          <t>study</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'study', 'label': 'Study'}</t>
+          <t>Study</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'travel_agency_1',_'label':_'travel_agency_1'}</t>
+          <t>travel_agency_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Travel Agency 1', 'label': 'Travel Agency 1'}</t>
+          <t>Travel Agency 1</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'travel_agency_2',_'label':_'travel_agency_2'}</t>
+          <t>travel_agency_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Travel Agency 2', 'label': 'Travel Agency 2'}</t>
+          <t>Travel Agency 2</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'travel_agency_3',_'label':_'travel_agency_3'}</t>
+          <t>travel_agency_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Travel Agency 3', 'label': 'Travel Agency 3'}</t>
+          <t>Travel Agency 3</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'type_1',_'label':_'type_1'}</t>
+          <t>type_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'type 1', 'label': 'Type 1'}</t>
+          <t>Type 1</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'type_2',_'label':_'type_2'}</t>
+          <t>type_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'type 2', 'label': 'Type 2'}</t>
+          <t>Type 2</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'type_3',_'label':_'type_3'}</t>
+          <t>type_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'type 3', 'label': 'Type 3'}</t>
+          <t>Type 3</t>
         </is>
       </c>
     </row>
